--- a/results/MHD/final_results.xlsx
+++ b/results/MHD/final_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,177 +485,111 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LinearRegression (Raw)</t>
+          <t>RandomForest (Raw)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.537651245959244</v>
+        <v>0.740438968485295</v>
       </c>
       <c r="C3" t="n">
-        <v>0.952653252439665</v>
+        <v>0.586992096438567</v>
       </c>
       <c r="D3" t="n">
-        <v>0.334</v>
+        <v>0.724</v>
       </c>
       <c r="E3" t="n">
-        <v>3712328951.533697</v>
+        <v>2781514653.538393</v>
       </c>
       <c r="F3" t="n">
-        <v>17.62523542085529</v>
+        <v>0.02671071043238361</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RandomForest (Raw)</t>
+          <t>GradientBoosting (DeepWalk-2)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.740438968485295</v>
+        <v>0.7455847887797977</v>
       </c>
       <c r="C4" t="n">
-        <v>0.586992096438567</v>
+        <v>0.6181571206423275</v>
       </c>
       <c r="D4" t="n">
-        <v>0.724</v>
+        <v>0.664</v>
       </c>
       <c r="E4" t="n">
-        <v>2781514653.538393</v>
+        <v>2753804741.754719</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02671071043238361</v>
+        <v>0.02775784868486615</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GradientBoosting (DeepWalk-5)</t>
+          <t>RandomForest (DeepWalk-2)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.758951165470966</v>
+        <v>0.7387882350640745</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6400213401722592</v>
+        <v>0.5720204963484657</v>
       </c>
       <c r="D5" t="n">
-        <v>0.666</v>
+        <v>0.704</v>
       </c>
       <c r="E5" t="n">
-        <v>2680489587.518554</v>
+        <v>2790345451.594701</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02782071844159046</v>
+        <v>0.02687120584980313</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LinearRegression (DeepWalk-5)</t>
+          <t>GradientBoosting (Node2Vec-5)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5504414876217146</v>
+        <v>0.7317512056473947</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9687926376849106</v>
+        <v>0.6186469445896194</v>
       </c>
       <c r="D6" t="n">
-        <v>0.348</v>
+        <v>0.664</v>
       </c>
       <c r="E6" t="n">
-        <v>3660620599.001607</v>
+        <v>2827681535.039186</v>
       </c>
       <c r="F6" t="n">
-        <v>17.61632384647313</v>
+        <v>0.02761794863571492</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RandomForest (DeepWalk-5)</t>
+          <t>RandomForest (Node2Vec-5)</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7333478464914268</v>
+        <v>0.7305807523634051</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5806270335833302</v>
+        <v>0.5702289547724625</v>
       </c>
       <c r="D7" t="n">
-        <v>0.698</v>
+        <v>0.71</v>
       </c>
       <c r="E7" t="n">
-        <v>2819253668.619368</v>
+        <v>2833843849.247606</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02864568268746838</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>GradientBoosting (Node2Vec-10)</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.7431726996860901</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.6269896200578715</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2766828240.793081</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.02796143725685607</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>LinearRegression (Node2Vec-10)</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.5665830269371193</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.9444469568553677</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.354</v>
-      </c>
-      <c r="E9" t="n">
-        <v>3594301994.63254</v>
-      </c>
-      <c r="F9" t="n">
-        <v>15.82914196036969</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>RandomForest (Node2Vec-10)</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0.7270480551524654</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.6034209440962212</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.712</v>
-      </c>
-      <c r="E10" t="n">
-        <v>2852362401.023149</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.02942609552456569</v>
+        <v>0.02702616519331684</v>
       </c>
     </row>
   </sheetData>

--- a/results/MHD/final_results.xlsx
+++ b/results/MHD/final_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,19 +511,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7455847887797977</v>
+        <v>0.7344442019565942</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6181571206423275</v>
+        <v>0.6245706616937912</v>
       </c>
       <c r="D4" t="n">
-        <v>0.664</v>
+        <v>0.676</v>
       </c>
       <c r="E4" t="n">
-        <v>2753804741.754719</v>
+        <v>2813451938.196763</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02775784868486615</v>
+        <v>0.0273767933826382</v>
       </c>
     </row>
     <row r="5">
@@ -533,19 +533,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7387882350640745</v>
+        <v>0.7403535766087865</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5720204963484657</v>
+        <v>0.5852280184438609</v>
       </c>
       <c r="D5" t="n">
-        <v>0.704</v>
+        <v>0.7</v>
       </c>
       <c r="E5" t="n">
-        <v>2790345451.594701</v>
+        <v>2781972155.233771</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02687120584980313</v>
+        <v>0.02686609660493999</v>
       </c>
     </row>
     <row r="6">
@@ -555,19 +555,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7317512056473947</v>
+        <v>0.7448238995261204</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6186469445896194</v>
+        <v>0.6201222491191668</v>
       </c>
       <c r="D6" t="n">
-        <v>0.664</v>
+        <v>0.676</v>
       </c>
       <c r="E6" t="n">
-        <v>2827681535.039186</v>
+        <v>2757919621.736633</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02761794863571492</v>
+        <v>0.02665060482716743</v>
       </c>
     </row>
     <row r="7">
@@ -577,19 +577,63 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7305807523634051</v>
+        <v>0.7489004638647561</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5702289547724625</v>
+        <v>0.5894952677721121</v>
       </c>
       <c r="D7" t="n">
-        <v>0.71</v>
+        <v>0.706</v>
       </c>
       <c r="E7" t="n">
-        <v>2833843849.247606</v>
+        <v>2735801363.957291</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02702616519331684</v>
+        <v>0.02682308487148268</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>GradientBoosting (Node2Vec-2)</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.7381662664493422</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.6159299809310885</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2793665507.688103</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.02727798284929917</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>RandomForest (Node2Vec-2)</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.7394769010327407</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.5764388386618275</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.708</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2786664751.805784</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0266461539598692</v>
       </c>
     </row>
   </sheetData>

--- a/results/MHD/final_results.xlsx
+++ b/results/MHD/final_results.xlsx
@@ -1,37 +1,84 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\mamintoosi-papers-codes\House2Vec\results\MHD\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30050B80-7EED-44D4-B693-41F8A097CF99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="525" yWindow="1440" windowWidth="11565" windowHeight="11340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
+  <si>
+    <t>Model</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>MAPE</t>
+  </si>
+  <si>
+    <t>Accuracy</t>
+  </si>
+  <si>
+    <t>RMSE</t>
+  </si>
+  <si>
+    <t>MSE_log</t>
+  </si>
+  <si>
+    <t>GradientBoosting (Raw)</t>
+  </si>
+  <si>
+    <t>RandomForest (Raw)</t>
+  </si>
+  <si>
+    <t>GradientBoosting (DeepWalk-ed2-nw50-wl15)</t>
+  </si>
+  <si>
+    <t>RandomForest (DeepWalk-ed2-nw50-wl15)</t>
+  </si>
+  <si>
+    <t>GradientBoosting (Node2Vec-ed2-nw50-wl15-p2.0-q1.0)</t>
+  </si>
+  <si>
+    <t>RandomForest (Node2Vec-ed2-nw50-wl15-p2.0-q1.0)</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +93,43 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,220 +417,191 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="56.28515625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>MAPE</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>RMSE</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>MSE_log</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>GradientBoosting (Raw)</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0.7380740349057346</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.6284376370066576</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.6860000000000001</v>
-      </c>
-      <c r="E2" t="n">
-        <v>2794157501.962305</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.02736639284375151</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>RandomForest (Raw)</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2">
+        <v>0.73807403490573464</v>
+      </c>
+      <c r="C2">
+        <v>0.62843763700665756</v>
+      </c>
+      <c r="D2">
+        <v>0.68600000000000005</v>
+      </c>
+      <c r="E2">
+        <v>2794157501.9623051</v>
+      </c>
+      <c r="F2">
+        <v>2.7366392843751509E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3">
         <v>0.740438968485295</v>
       </c>
-      <c r="C3" t="n">
-        <v>0.586992096438567</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.724</v>
-      </c>
-      <c r="E3" t="n">
+      <c r="C3">
+        <v>0.58699209643856698</v>
+      </c>
+      <c r="D3">
+        <v>0.72399999999999998</v>
+      </c>
+      <c r="E3">
         <v>2781514653.538393</v>
       </c>
-      <c r="F3" t="n">
-        <v>0.02671071043238361</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>GradientBoosting (DeepWalk-2)</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0.7344442019565942</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.6245706616937912</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.676</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2813451938.196763</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.0273767933826382</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>RandomForest (DeepWalk-2)</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0.7403535766087865</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.5852280184438609</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2781972155.233771</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.02686609660493999</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>GradientBoosting (Node2Vec-5)</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.7448238995261204</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.6201222491191668</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.676</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2757919621.736633</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.02665060482716743</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>RandomForest (Node2Vec-5)</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.7489004638647561</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.5894952677721121</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.706</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2735801363.957291</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.02682308487148268</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>GradientBoosting (Node2Vec-2)</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.7381662664493422</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.6159299809310885</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.676</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2793665507.688103</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.02727798284929917</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>RandomForest (Node2Vec-2)</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.7394769010327407</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.5764388386618275</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.708</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2786664751.805784</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.0266461539598692</v>
+      <c r="F3">
+        <v>2.671071043238361E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>0.73826042433380257</v>
+      </c>
+      <c r="C4">
+        <v>0.62659593883826548</v>
+      </c>
+      <c r="D4">
+        <v>0.68200000000000005</v>
+      </c>
+      <c r="E4">
+        <v>2793163148.2648101</v>
+      </c>
+      <c r="F4">
+        <v>2.79500171996367E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>0.73858007879661425</v>
+      </c>
+      <c r="C5">
+        <v>0.57766128268056882</v>
+      </c>
+      <c r="D5">
+        <v>0.71199999999999997</v>
+      </c>
+      <c r="E5">
+        <v>2791457025.2384071</v>
+      </c>
+      <c r="F5">
+        <v>2.7570336250752239E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>0.72733936613983519</v>
+      </c>
+      <c r="C6">
+        <v>0.63510278192368075</v>
+      </c>
+      <c r="D6">
+        <v>0.67800000000000005</v>
+      </c>
+      <c r="E6">
+        <v>2850839886.9967771</v>
+      </c>
+      <c r="F6">
+        <v>2.801743495487621E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7">
+        <v>0.7361855194495398</v>
+      </c>
+      <c r="C7">
+        <v>0.58253582639683332</v>
+      </c>
+      <c r="D7">
+        <v>0.69599999999999995</v>
+      </c>
+      <c r="E7">
+        <v>2804212503.8920088</v>
+      </c>
+      <c r="F7">
+        <v>2.6570116241055791E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>0.73800336522958365</v>
+      </c>
+      <c r="C8">
+        <v>0.61104338676597347</v>
+      </c>
+      <c r="D8">
+        <v>0.68</v>
+      </c>
+      <c r="E8">
+        <v>2794534419.3257499</v>
+      </c>
+      <c r="F8">
+        <v>2.7617460149049741E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9">
+        <v>0.73978300797152585</v>
+      </c>
+      <c r="C9">
+        <v>0.58630054737232518</v>
+      </c>
+      <c r="D9">
+        <v>0.69599999999999995</v>
+      </c>
+      <c r="E9">
+        <v>2785027146.282795</v>
+      </c>
+      <c r="F9">
+        <v>2.7003900031736972E-2</v>
       </c>
     </row>
   </sheetData>

--- a/results/MHD/final_results.xlsx
+++ b/results/MHD/final_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\mamintoosi-papers-codes\House2Vec\results\MHD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30050B80-7EED-44D4-B693-41F8A097CF99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFCDB172-83FB-4F66-9AFC-3BB34FE831DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="525" yWindow="1440" windowWidth="11565" windowHeight="11340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14970" yWindow="1575" windowWidth="11565" windowHeight="11340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -46,16 +46,16 @@
     <t>RandomForest (Raw)</t>
   </si>
   <si>
-    <t>GradientBoosting (DeepWalk-ed2-nw50-wl15)</t>
-  </si>
-  <si>
-    <t>RandomForest (DeepWalk-ed2-nw50-wl15)</t>
-  </si>
-  <si>
-    <t>GradientBoosting (Node2Vec-ed2-nw50-wl15-p2.0-q1.0)</t>
-  </si>
-  <si>
-    <t>RandomForest (Node2Vec-ed2-nw50-wl15-p2.0-q1.0)</t>
+    <t>GradientBoosting (DeepWalk-ed2-nw80-wl15)</t>
+  </si>
+  <si>
+    <t>RandomForest (DeepWalk-ed2-nw80-wl15)</t>
+  </si>
+  <si>
+    <t>GradientBoosting (Node2Vec-ed2-nw80-wl15-p3-q1)</t>
+  </si>
+  <si>
+    <t>RandomForest (Node2Vec-ed2-nw80-wl15-p3-q1)</t>
   </si>
 </sst>
 </file>
@@ -421,7 +421,8 @@
   <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="56.28515625" customWidth="1"/>
+    <col min="1" max="1" width="41.140625" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -489,19 +490,19 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>0.73826042433380257</v>
+        <v>0.74523806281954197</v>
       </c>
       <c r="C4">
-        <v>0.62659593883826548</v>
+        <v>0.62821055256256164</v>
       </c>
       <c r="D4">
-        <v>0.68200000000000005</v>
+        <v>0.69</v>
       </c>
       <c r="E4">
-        <v>2793163148.2648101</v>
+        <v>2755680593.627563</v>
       </c>
       <c r="F4">
-        <v>2.79500171996367E-2</v>
+        <v>2.708648409366754E-2</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -509,19 +510,19 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>0.73858007879661425</v>
+        <v>0.73940195059582203</v>
       </c>
       <c r="C5">
-        <v>0.57766128268056882</v>
+        <v>0.58627201091134784</v>
       </c>
       <c r="D5">
-        <v>0.71199999999999997</v>
+        <v>0.70599999999999996</v>
       </c>
       <c r="E5">
-        <v>2791457025.2384071</v>
+        <v>2787065573.6939659</v>
       </c>
       <c r="F5">
-        <v>2.7570336250752239E-2</v>
+        <v>2.6963851903443099E-2</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -529,19 +530,19 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>0.72733936613983519</v>
+        <v>0.73834972324777892</v>
       </c>
       <c r="C6">
-        <v>0.63510278192368075</v>
+        <v>0.61687467858744049</v>
       </c>
       <c r="D6">
-        <v>0.67800000000000005</v>
+        <v>0.67600000000000005</v>
       </c>
       <c r="E6">
-        <v>2850839886.9967771</v>
+        <v>2792686629.3562932</v>
       </c>
       <c r="F6">
-        <v>2.801743495487621E-2</v>
+        <v>2.7502607410834729E-2</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -549,19 +550,19 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>0.7361855194495398</v>
+        <v>0.74580045574477116</v>
       </c>
       <c r="C7">
-        <v>0.58253582639683332</v>
+        <v>0.57240566889975841</v>
       </c>
       <c r="D7">
-        <v>0.69599999999999995</v>
+        <v>0.72</v>
       </c>
       <c r="E7">
-        <v>2804212503.8920088</v>
+        <v>2752637298.5344548</v>
       </c>
       <c r="F7">
-        <v>2.6570116241055791E-2</v>
+        <v>2.6766367310377868E-2</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -569,19 +570,19 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>0.73800336522958365</v>
+        <v>0.72945015126561974</v>
       </c>
       <c r="C8">
-        <v>0.61104338676597347</v>
+        <v>0.63426387480553403</v>
       </c>
       <c r="D8">
-        <v>0.68</v>
+        <v>0.66200000000000003</v>
       </c>
       <c r="E8">
-        <v>2794534419.3257499</v>
+        <v>2839783648.9060922</v>
       </c>
       <c r="F8">
-        <v>2.7617460149049741E-2</v>
+        <v>2.84431535467079E-2</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -589,19 +590,19 @@
         <v>11</v>
       </c>
       <c r="B9">
-        <v>0.73978300797152585</v>
+        <v>0.7444508304895191</v>
       </c>
       <c r="C9">
-        <v>0.58630054737232518</v>
+        <v>0.56457959434684113</v>
       </c>
       <c r="D9">
-        <v>0.69599999999999995</v>
+        <v>0.72599999999999998</v>
       </c>
       <c r="E9">
-        <v>2785027146.282795</v>
+        <v>2759934933.175571</v>
       </c>
       <c r="F9">
-        <v>2.7003900031736972E-2</v>
+        <v>2.662473290981035E-2</v>
       </c>
     </row>
   </sheetData>

--- a/results/MHD/final_results.xlsx
+++ b/results/MHD/final_results.xlsx
@@ -1,84 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\mamintoosi-papers-codes\House2Vec\results\MHD\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFCDB172-83FB-4F66-9AFC-3BB34FE831DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="14970" yWindow="1575" windowWidth="11565" windowHeight="11340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
-  <si>
-    <t>Model</t>
-  </si>
-  <si>
-    <t>R2</t>
-  </si>
-  <si>
-    <t>MAPE</t>
-  </si>
-  <si>
-    <t>Accuracy</t>
-  </si>
-  <si>
-    <t>RMSE</t>
-  </si>
-  <si>
-    <t>MSE_log</t>
-  </si>
-  <si>
-    <t>GradientBoosting (Raw)</t>
-  </si>
-  <si>
-    <t>RandomForest (Raw)</t>
-  </si>
-  <si>
-    <t>GradientBoosting (DeepWalk-ed2-nw80-wl15)</t>
-  </si>
-  <si>
-    <t>RandomForest (DeepWalk-ed2-nw80-wl15)</t>
-  </si>
-  <si>
-    <t>GradientBoosting (Node2Vec-ed2-nw80-wl15-p3-q1)</t>
-  </si>
-  <si>
-    <t>RandomForest (Node2Vec-ed2-nw80-wl15-p3-q1)</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -93,43 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -417,192 +420,220 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="41.140625" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" customWidth="1"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2">
-        <v>0.73807403490573464</v>
-      </c>
-      <c r="C2">
-        <v>0.62843763700665756</v>
-      </c>
-      <c r="D2">
-        <v>0.68600000000000005</v>
-      </c>
-      <c r="E2">
-        <v>2794157501.9623051</v>
-      </c>
-      <c r="F2">
-        <v>2.7366392843751509E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>MAPE</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Accuracy</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>MSE_log</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>GradientBoosting (Raw)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.7380740349057346</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.6284376370066576</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.6860000000000001</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2794157501.962305</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.02736639284375151</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>RandomForest (Raw)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>0.740438968485295</v>
       </c>
-      <c r="C3">
-        <v>0.58699209643856698</v>
-      </c>
-      <c r="D3">
-        <v>0.72399999999999998</v>
-      </c>
-      <c r="E3">
+      <c r="C3" t="n">
+        <v>0.586992096438567</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="E3" t="n">
         <v>2781514653.538393</v>
       </c>
-      <c r="F3">
-        <v>2.671071043238361E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4">
-        <v>0.74523806281954197</v>
-      </c>
-      <c r="C4">
-        <v>0.62821055256256164</v>
-      </c>
-      <c r="D4">
-        <v>0.69</v>
-      </c>
-      <c r="E4">
-        <v>2755680593.627563</v>
-      </c>
-      <c r="F4">
-        <v>2.708648409366754E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5">
-        <v>0.73940195059582203</v>
-      </c>
-      <c r="C5">
-        <v>0.58627201091134784</v>
-      </c>
-      <c r="D5">
-        <v>0.70599999999999996</v>
-      </c>
-      <c r="E5">
-        <v>2787065573.6939659</v>
-      </c>
-      <c r="F5">
-        <v>2.6963851903443099E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6">
-        <v>0.73834972324777892</v>
-      </c>
-      <c r="C6">
-        <v>0.61687467858744049</v>
-      </c>
-      <c r="D6">
-        <v>0.67600000000000005</v>
-      </c>
-      <c r="E6">
-        <v>2792686629.3562932</v>
-      </c>
-      <c r="F6">
-        <v>2.7502607410834729E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7">
-        <v>0.74580045574477116</v>
-      </c>
-      <c r="C7">
-        <v>0.57240566889975841</v>
-      </c>
-      <c r="D7">
-        <v>0.72</v>
-      </c>
-      <c r="E7">
-        <v>2752637298.5344548</v>
-      </c>
-      <c r="F7">
-        <v>2.6766367310377868E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>0.72945015126561974</v>
-      </c>
-      <c r="C8">
-        <v>0.63426387480553403</v>
-      </c>
-      <c r="D8">
-        <v>0.66200000000000003</v>
-      </c>
-      <c r="E8">
-        <v>2839783648.9060922</v>
-      </c>
-      <c r="F8">
-        <v>2.84431535467079E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9">
-        <v>0.7444508304895191</v>
-      </c>
-      <c r="C9">
-        <v>0.56457959434684113</v>
-      </c>
-      <c r="D9">
-        <v>0.72599999999999998</v>
-      </c>
-      <c r="E9">
-        <v>2759934933.175571</v>
-      </c>
-      <c r="F9">
-        <v>2.662473290981035E-2</v>
+      <c r="F3" t="n">
+        <v>0.02671071043238361</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>GradientBoosting (DeepWalk-ed2-nw80-wl20)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.7374761755798038</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.6156260865368498</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2797344587.573833</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.02687877291779962</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>RandomForest (DeepWalk-ed2-nw80-wl20)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.7322272670454327</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.5877296882117926</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.696</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2825171276.210193</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.02682295937982092</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>GradientBoosting (Node2Vec-ed2-nw80-wl20-p3-q1)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.7386904107933016</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.603972160528364</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.668</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2790867897.353467</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.02734067595375386</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>RandomForest (Node2Vec-ed2-nw80-wl20-p3-q1)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.7400298715775899</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.5711653501827127</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2783705777.95759</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.02671736061126825</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>GradientBoosting (Node2Vec-ed2-nw80-wl20-p3-q1)</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.7417415083746519</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.6195713638317739</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2774526719.866329</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.02754009256237435</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>RandomForest (Node2Vec-ed2-nw80-wl20-p3-q1)</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.739811618105337</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.5705545659653197</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2784874039.083741</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.02662958052099725</v>
       </c>
     </row>
   </sheetData>

--- a/results/MHD/final_results.xlsx
+++ b/results/MHD/final_results.xlsx
@@ -489,19 +489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.740438968485295</v>
+        <v>0.7399241426074452</v>
       </c>
       <c r="C3" t="n">
-        <v>0.586992096438567</v>
+        <v>0.5872282759404527</v>
       </c>
       <c r="D3" t="n">
-        <v>0.724</v>
+        <v>0.726</v>
       </c>
       <c r="E3" t="n">
-        <v>2781514653.538393</v>
+        <v>2784271782.268144</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02671071043238361</v>
+        <v>0.02675527111976066</v>
       </c>
     </row>
     <row r="4">
@@ -511,19 +511,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7374761755798038</v>
+        <v>0.7414358858020444</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6156260865368498</v>
+        <v>0.6406999088403355</v>
       </c>
       <c r="D4" t="n">
-        <v>0.676</v>
+        <v>0.68</v>
       </c>
       <c r="E4" t="n">
-        <v>2797344587.573833</v>
+        <v>2776167919.094565</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02687877291779962</v>
+        <v>0.02782192426535958</v>
       </c>
     </row>
     <row r="5">
@@ -533,19 +533,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7322272670454327</v>
+        <v>0.7334038789462616</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5877296882117926</v>
+        <v>0.7425763902811812</v>
       </c>
       <c r="D5" t="n">
-        <v>0.696</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>2825171276.210193</v>
+        <v>2818957443.741159</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02682295937982092</v>
+        <v>0.02848402201675061</v>
       </c>
     </row>
     <row r="6">
@@ -555,19 +555,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7386904107933016</v>
+        <v>0.7405076240179609</v>
       </c>
       <c r="C6" t="n">
-        <v>0.603972160528364</v>
+        <v>0.6242047416219553</v>
       </c>
       <c r="D6" t="n">
-        <v>0.668</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>2790867897.353467</v>
+        <v>2781146765.110255</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02734067595375386</v>
+        <v>0.02750280136730992</v>
       </c>
     </row>
     <row r="7">
@@ -577,63 +577,63 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7400298715775899</v>
+        <v>0.7426199631070147</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5711653501827127</v>
+        <v>0.6346723232489212</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>2783705777.95759</v>
+        <v>2769803986.00248</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02671736061126825</v>
+        <v>0.02774426308220772</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GradientBoosting (Node2Vec-ed2-nw80-wl20-p3-q1)</t>
+          <t>GradientBoosting (Node2Vec-ed5-nw80-wl20-p3-q1)</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7417415083746519</v>
+        <v>0.713081235746492</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6195713638317739</v>
+        <v>0.6862432246908932</v>
       </c>
       <c r="D8" t="n">
-        <v>0.68</v>
+        <v>0.654</v>
       </c>
       <c r="E8" t="n">
-        <v>2774526719.866329</v>
+        <v>2924429002.983551</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02754009256237435</v>
+        <v>0.02884435161761052</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>RandomForest (Node2Vec-ed2-nw80-wl20-p3-q1)</t>
+          <t>RandomForest (Node2Vec-ed5-nw80-wl20-p3-q1)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.739811618105337</v>
+        <v>0.7437561681063232</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5705545659653197</v>
+        <v>0.6881128993387209</v>
       </c>
       <c r="D9" t="n">
-        <v>0.714</v>
+        <v>0.698</v>
       </c>
       <c r="E9" t="n">
-        <v>2784874039.083741</v>
+        <v>2763683569.586885</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02662958052099725</v>
+        <v>0.02795021927041677</v>
       </c>
     </row>
   </sheetData>

--- a/results/MHD/final_results.xlsx
+++ b/results/MHD/final_results.xlsx
@@ -507,133 +507,133 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GradientBoosting (DeepWalk-ed2-nw80-wl20)</t>
+          <t>GradientBoosting (DeepWalk-ed2-nw50-wl15)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7414358858020444</v>
+        <v>0.7302231717817118</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6406999088403355</v>
+        <v>0.6674244509602734</v>
       </c>
       <c r="D4" t="n">
-        <v>0.68</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>2776167919.094565</v>
+        <v>2835723803.138944</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02782192426535958</v>
+        <v>0.02831571736111676</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RandomForest (DeepWalk-ed2-nw80-wl20)</t>
+          <t>RandomForest (DeepWalk-ed2-nw50-wl15)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7334038789462616</v>
+        <v>0.7555748666142387</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7425763902811812</v>
+        <v>0.6600218495337481</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.71</v>
       </c>
       <c r="E5" t="n">
-        <v>2818957443.741159</v>
+        <v>2699196716.584015</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02848402201675061</v>
+        <v>0.0272528214324642</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GradientBoosting (Node2Vec-ed2-nw80-wl20-p3-q1)</t>
+          <t>GradientBoosting (Node2Vec-ed2-nw50-wl15-p1-q1)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7405076240179609</v>
+        <v>0.744107815877375</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6242047416219553</v>
+        <v>0.6204936862576729</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.674</v>
       </c>
       <c r="E6" t="n">
-        <v>2781146765.110255</v>
+        <v>2761786593.554024</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02750280136730992</v>
+        <v>0.02663517863164721</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RandomForest (Node2Vec-ed2-nw80-wl20-p3-q1)</t>
+          <t>RandomForest (Node2Vec-ed2-nw50-wl15-p1-q1)</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7426199631070147</v>
+        <v>0.7516230224938352</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6346723232489212</v>
+        <v>0.6303639371841142</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.696</v>
       </c>
       <c r="E7" t="n">
-        <v>2769803986.00248</v>
+        <v>2720929413.613901</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02774426308220772</v>
+        <v>0.02717314328606066</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GradientBoosting (Node2Vec-ed5-nw80-wl20-p3-q1)</t>
+          <t>GradientBoosting (Node2Vec-ed2-nw50-wl15-p3-q1)</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.713081235746492</v>
+        <v>0.7537893154201518</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6862432246908932</v>
+        <v>0.6487520864641012</v>
       </c>
       <c r="D8" t="n">
-        <v>0.654</v>
+        <v>0.67</v>
       </c>
       <c r="E8" t="n">
-        <v>2924429002.983551</v>
+        <v>2709037734.200227</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02884435161761052</v>
+        <v>0.02769804620997102</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>RandomForest (Node2Vec-ed5-nw80-wl20-p3-q1)</t>
+          <t>RandomForest (Node2Vec-ed2-nw50-wl15-p3-q1)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7437561681063232</v>
+        <v>0.7591807817977216</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6881128993387209</v>
+        <v>0.6376320446505731</v>
       </c>
       <c r="D9" t="n">
-        <v>0.698</v>
+        <v>0.702</v>
       </c>
       <c r="E9" t="n">
-        <v>2763683569.586885</v>
+        <v>2679212603.920464</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02795021927041677</v>
+        <v>0.0271030865278058</v>
       </c>
     </row>
   </sheetData>

--- a/results/MHD/final_results.xlsx
+++ b/results/MHD/final_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,177 +463,45 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GradientBoosting (Raw)</t>
+          <t>GradientBoosting (Node2Vec-ed2-nw50-wl15-p3-q1)</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7380740349057346</v>
+        <v>0.742224431486459</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6284376370066576</v>
+        <v>0.6367380749024879</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="E2" t="n">
-        <v>2794157501.962305</v>
+        <v>2771931432.438838</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02736639284375151</v>
+        <v>0.02692355213803288</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RandomForest (Raw)</t>
+          <t>RandomForest (Node2Vec-ed2-nw50-wl15-p3-q1)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7399241426074452</v>
+        <v>0.7423995105203118</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5872282759404527</v>
+        <v>0.7152178671562467</v>
       </c>
       <c r="D3" t="n">
-        <v>0.726</v>
+        <v>0.706</v>
       </c>
       <c r="E3" t="n">
-        <v>2784271782.268144</v>
+        <v>2770989936.0976</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02675527111976066</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>GradientBoosting (DeepWalk-ed2-nw50-wl15)</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0.7302231717817118</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.6674244509602734</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.6879999999999999</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2835723803.138944</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.02831571736111676</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>RandomForest (DeepWalk-ed2-nw50-wl15)</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0.7555748666142387</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.6600218495337481</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2699196716.584015</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.0272528214324642</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>GradientBoosting (Node2Vec-ed2-nw50-wl15-p1-q1)</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.744107815877375</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.6204936862576729</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.674</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2761786593.554024</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.02663517863164721</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>RandomForest (Node2Vec-ed2-nw50-wl15-p1-q1)</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.7516230224938352</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.6303639371841142</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.696</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2720929413.613901</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.02717314328606066</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>GradientBoosting (Node2Vec-ed2-nw50-wl15-p3-q1)</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.7537893154201518</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.6487520864641012</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2709037734.200227</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.02769804620997102</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>RandomForest (Node2Vec-ed2-nw50-wl15-p3-q1)</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.7591807817977216</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.6376320446505731</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.702</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2679212603.920464</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.0271030865278058</v>
+        <v>0.02842455396703874</v>
       </c>
     </row>
   </sheetData>

--- a/results/MHD/final_results.xlsx
+++ b/results/MHD/final_results.xlsx
@@ -463,45 +463,45 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GradientBoosting (Node2Vec-ed2-nw50-wl15-p3-q1)</t>
+          <t>GradientBoosting (Node2Vec-ed5-nw50-wl15-p3-q1)</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.742224431486459</v>
+        <v>0.7266782664431117</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6367380749024879</v>
+        <v>0.6471268132144444</v>
       </c>
       <c r="D2" t="n">
-        <v>0.68</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>2771931432.438838</v>
+        <v>2854293902.937426</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02692355213803288</v>
+        <v>0.02816493074437523</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RandomForest (Node2Vec-ed2-nw50-wl15-p3-q1)</t>
+          <t>RandomForest (Node2Vec-ed5-nw50-wl15-p3-q1)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7423995105203118</v>
+        <v>0.7232989684702824</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7152178671562467</v>
+        <v>0.6732609712822674</v>
       </c>
       <c r="D3" t="n">
-        <v>0.706</v>
+        <v>0.708</v>
       </c>
       <c r="E3" t="n">
-        <v>2770989936.0976</v>
+        <v>2871884671.437892</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02842455396703874</v>
+        <v>0.02833004196969095</v>
       </c>
     </row>
   </sheetData>

--- a/results/MHD/final_results.xlsx
+++ b/results/MHD/final_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,177 +485,111 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LinearRegression (Raw)</t>
+          <t>RandomForest (Raw)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.537651245959244</v>
+        <v>0.740438968485295</v>
       </c>
       <c r="C3" t="n">
-        <v>0.952653252439665</v>
+        <v>0.586992096438567</v>
       </c>
       <c r="D3" t="n">
-        <v>0.334</v>
+        <v>0.724</v>
       </c>
       <c r="E3" t="n">
-        <v>3712328951.533697</v>
+        <v>2781514653.538393</v>
       </c>
       <c r="F3" t="n">
-        <v>17.62523542085529</v>
+        <v>0.02671071043238361</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RandomForest (Raw)</t>
+          <t>GradientBoosting (DeepWalk-10)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.740438968485295</v>
+        <v>0.7330598475152048</v>
       </c>
       <c r="C4" t="n">
-        <v>0.586992096438567</v>
+        <v>0.6472285685056548</v>
       </c>
       <c r="D4" t="n">
-        <v>0.724</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>2781514653.538393</v>
+        <v>2820775732.18114</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02671071043238361</v>
+        <v>0.030823254917073</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GradientBoosting (DeepWalk-5)</t>
+          <t>RandomForest (DeepWalk-10)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.758951165470966</v>
+        <v>0.7312705044847815</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6400213401722592</v>
+        <v>0.5848333068565812</v>
       </c>
       <c r="D5" t="n">
-        <v>0.666</v>
+        <v>0.722</v>
       </c>
       <c r="E5" t="n">
-        <v>2680489587.518554</v>
+        <v>2830214000.092139</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02782071844159046</v>
+        <v>0.02846475700361299</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LinearRegression (DeepWalk-5)</t>
+          <t>GradientBoosting (Node2Vec-2)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5504414876217146</v>
+        <v>0.7308800301153628</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9687926376849106</v>
+        <v>0.6458150802919591</v>
       </c>
       <c r="D6" t="n">
-        <v>0.348</v>
+        <v>0.664</v>
       </c>
       <c r="E6" t="n">
-        <v>3660620599.001607</v>
+        <v>2832269458.999894</v>
       </c>
       <c r="F6" t="n">
-        <v>17.61632384647313</v>
+        <v>0.02823405146759362</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RandomForest (DeepWalk-5)</t>
+          <t>RandomForest (Node2Vec-2)</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7333478464914268</v>
+        <v>0.7354812754172072</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5806270335833302</v>
+        <v>0.6237690035147908</v>
       </c>
       <c r="D7" t="n">
-        <v>0.698</v>
+        <v>0.704</v>
       </c>
       <c r="E7" t="n">
-        <v>2819253668.619368</v>
+        <v>2807952885.625758</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02864568268746838</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>GradientBoosting (Node2Vec-10)</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.7431726996860901</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.6269896200578715</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2766828240.793081</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.02796143725685607</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>LinearRegression (Node2Vec-10)</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.5665830269371193</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.9444469568553677</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.354</v>
-      </c>
-      <c r="E9" t="n">
-        <v>3594301994.63254</v>
-      </c>
-      <c r="F9" t="n">
-        <v>15.82914196036969</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>RandomForest (Node2Vec-10)</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0.7270480551524654</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.6034209440962212</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.712</v>
-      </c>
-      <c r="E10" t="n">
-        <v>2852362401.023149</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.02942609552456569</v>
+        <v>0.0275921343554554</v>
       </c>
     </row>
   </sheetData>
